--- a/Tables/G_ObjSaleInfoTable.xlsx
+++ b/Tables/G_ObjSaleInfoTable.xlsx
@@ -379,8 +379,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.88"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
-    <col customWidth="1" min="9" max="9" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" min="7" max="7" width="7.63"/>
+    <col customWidth="1" min="8" max="8" width="10.5"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11264,7 +11270,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.88"/>
-    <col customWidth="1" min="2" max="9" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" min="7" max="7" width="7.63"/>
+    <col customWidth="1" min="8" max="8" width="10.5"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21368,7 +21381,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.88"/>
-    <col customWidth="1" min="2" max="9" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" min="7" max="7" width="7.63"/>
+    <col customWidth="1" min="8" max="8" width="10.5"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31472,7 +31492,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="18.75"/>
-    <col customWidth="1" min="2" max="9" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" min="7" max="7" width="7.63"/>
+    <col customWidth="1" min="8" max="8" width="10.5"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41576,7 +41603,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="20.13"/>
-    <col customWidth="1" min="2" max="9" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="11.75"/>
+    <col customWidth="1" min="7" max="7" width="7.63"/>
+    <col customWidth="1" min="8" max="8" width="10.5"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
